--- a/Result/profitability/8024.xlsx
+++ b/Result/profitability/8024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.43625</v>
+        <v>-0.40375</v>
       </c>
       <c r="N2" t="n">
-        <v>24.94125</v>
+        <v>24.4325</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2812500000000001</v>
+        <v>-0.2825</v>
       </c>
       <c r="N3" t="n">
-        <v>24.68875</v>
+        <v>24.70625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.72</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1675</v>
+        <v>-0.12375</v>
       </c>
       <c r="N4" t="n">
-        <v>24.98375</v>
+        <v>27.00875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09750000000000002</v>
+        <v>-0.01500000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>26.2325</v>
+        <v>27.7875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02499999999999998</v>
+        <v>0.07124999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>27.6125</v>
+        <v>30.08625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1575</v>
+        <v>0.205</v>
       </c>
       <c r="N7" t="n">
-        <v>30.05875</v>
+        <v>31.16875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.29375</v>
+        <v>0.3374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>31.51</v>
+        <v>31.83375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.03</v>
       </c>
       <c r="M11" t="n">
-        <v>0.435</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>32.82</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>70</v>
+      </c>
+      <c r="D75" t="n">
+        <v>48</v>
+      </c>
+      <c r="E75" t="n">
+        <v>23</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-17.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4950000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.28375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6363636363636364</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08723475917817436</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7674418604651163</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6270161290322582</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
